--- a/data/Terre di Pedemonte/investment_decision/Verscio_SFH_from_2015_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Verscio_SFH_from_2015_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>56.24885622269773</v>
+        <v>54.68790407854311</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>9139.662253522103</v>
       </c>
       <c r="F4" t="n">
-        <v>67.13135028290505</v>
+        <v>54.11658943545771</v>
       </c>
       <c r="G4" t="n">
         <v>9139.662253522103</v>
       </c>
       <c r="H4" t="n">
-        <v>56.7350784</v>
+        <v>54.68790407854308</v>
       </c>
       <c r="I4" t="n">
         <v>9139.662253522103</v>
       </c>
       <c r="J4" t="n">
-        <v>65.68257455123168</v>
+        <v>54.51406452096003</v>
       </c>
       <c r="K4" t="n">
         <v>9139.662253522103</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>63.74856462784597</v>
+        <v>60.68178023169208</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>9139.662253522103</v>
       </c>
       <c r="F5" t="n">
-        <v>70.39865082708998</v>
+        <v>60.72401233155808</v>
       </c>
       <c r="G5" t="n">
         <v>9139.662253522103</v>
       </c>
       <c r="H5" t="n">
-        <v>63.7485647223645</v>
+        <v>60.66363787294497</v>
       </c>
       <c r="I5" t="n">
         <v>9139.662253522103</v>
       </c>
       <c r="J5" t="n">
-        <v>70.39865082708998</v>
+        <v>60.58295461161253</v>
       </c>
       <c r="K5" t="n">
         <v>9139.662253522103</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>69.88743345422719</v>
+        <v>60.68178023169208</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>9139.662253522103</v>
       </c>
       <c r="F6" t="n">
-        <v>70.5748309260396</v>
+        <v>60.72401233155808</v>
       </c>
       <c r="G6" t="n">
         <v>9139.662253522103</v>
       </c>
       <c r="H6" t="n">
-        <v>69.88743358643673</v>
+        <v>60.66363787294497</v>
       </c>
       <c r="I6" t="n">
         <v>9139.662253522103</v>
       </c>
       <c r="J6" t="n">
-        <v>70.5748309260396</v>
+        <v>60.58295461161253</v>
       </c>
       <c r="K6" t="n">
         <v>9139.662253522103</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>13.70949338028315</v>
+        <v>27.82619325842697</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.004052505600000001</v>
+        <v>0.001895209702051895</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.004052505600000001</v>
+        <v>0.001668678776470588</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.004052505600000001</v>
+        <v>0.001893389122857735</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.004052505600000001</v>
+        <v>0.001668678776470588</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.004052505600000001</v>
+        <v>0.002560849891743439</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004052505600000001</v>
+        <v>0.002622209505882353</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.004052505600000001</v>
+        <v>0.002622209505882353</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.004052505600000001</v>
+        <v>0.002622209505882353</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.005482801694117647</v>
+        <v>0.004290888282352942</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005482801694117647</v>
+        <v>0.004498902419042156</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.005482801694117647</v>
+        <v>0.004290888282352942</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.005482801694117647</v>
+        <v>0.004354182801285255</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.005624873349515825</v>
+        <v>0.004529270964705882</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.005721184376470589</v>
+        <v>0.004529270964705882</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.005624873357855694</v>
+        <v>0.004290888282352942</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.005721184376470589</v>
+        <v>0.004354182801285255</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.005721184376470589</v>
+        <v>0.004529270964705882</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005721184376470589</v>
+        <v>0.004529270964705882</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.005721184376470589</v>
+        <v>0.004290888282352942</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.005721184376470589</v>
+        <v>0.004354182801285255</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>2.2926608</v>
+        <v>2.25326334456658</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>4.255130879999999</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2926608</v>
+        <v>2.263401110116145</v>
       </c>
       <c r="G19" t="n">
         <v>4.255130879999999</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2926608</v>
+        <v>2.007515044815353</v>
       </c>
       <c r="I19" t="n">
         <v>4.255130879999999</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2926608</v>
+        <v>2.005176646317718</v>
       </c>
       <c r="K19" t="n">
         <v>4.255130879999999</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>3.2926608</v>
+        <v>2.303220362262385</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>4.255130879999999</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2926608</v>
+        <v>2.363925816733139</v>
       </c>
       <c r="G20" t="n">
         <v>4.255130879999999</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2926608</v>
+        <v>2.057259686475315</v>
       </c>
       <c r="I20" t="n">
         <v>4.255130879999999</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2926608</v>
+        <v>2.057365780784999</v>
       </c>
       <c r="K20" t="n">
         <v>4.255130879999999</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>3.2926608</v>
+        <v>2.303220362262385</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>4.255130879999999</v>
       </c>
       <c r="F21" t="n">
-        <v>3.2926608</v>
+        <v>2.363925816733139</v>
       </c>
       <c r="G21" t="n">
         <v>4.255130879999999</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2926608</v>
+        <v>2.057259686475315</v>
       </c>
       <c r="I21" t="n">
         <v>4.255130879999999</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2926608</v>
+        <v>2.057365780784999</v>
       </c>
       <c r="K21" t="n">
         <v>4.255130879999999</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.03939745543341993</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>4.255130879999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.0292596898838548</v>
       </c>
       <c r="G29" t="n">
         <v>4.255130879999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.2851457551846467</v>
       </c>
       <c r="I29" t="n">
         <v>4.255130879999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.2874841536822819</v>
       </c>
       <c r="K29" t="n">
         <v>4.255130879999999</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.9894404377376146</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>4.255130879999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.9287349832668612</v>
       </c>
       <c r="G30" t="n">
         <v>4.255130879999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.235401113524685</v>
       </c>
       <c r="I30" t="n">
         <v>4.255130879999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.235295019215001</v>
       </c>
       <c r="K30" t="n">
         <v>4.255130879999999</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.9894404377376146</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>4.255130879999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.9287349832668612</v>
       </c>
       <c r="G31" t="n">
         <v>4.255130879999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1.235401113524685</v>
       </c>
       <c r="I31" t="n">
         <v>4.255130879999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.235295019215001</v>
       </c>
       <c r="K31" t="n">
         <v>4.255130879999999</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>1.340130894308567</v>
+        <v>1.37428539195226</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>16.55121768438931</v>
       </c>
       <c r="F54" t="n">
-        <v>1.340130894308567</v>
+        <v>1.191019404763469</v>
       </c>
       <c r="G54" t="n">
         <v>16.55121768438931</v>
       </c>
       <c r="H54" t="n">
-        <v>1.231109736146335</v>
+        <v>1.366745726947695</v>
       </c>
       <c r="I54" t="n">
         <v>16.55121768438931</v>
       </c>
       <c r="J54" t="n">
-        <v>1.239368886370305</v>
+        <v>1.199880202547027</v>
       </c>
       <c r="K54" t="n">
         <v>16.55121768438931</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>3.069807790763183</v>
+        <v>3.007584976284879</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>16.55121768438931</v>
       </c>
       <c r="F55" t="n">
-        <v>3.069807790763183</v>
+        <v>2.728359084910181</v>
       </c>
       <c r="G55" t="n">
         <v>16.55121768438931</v>
       </c>
       <c r="H55" t="n">
-        <v>2.822386787934255</v>
+        <v>2.974723071696799</v>
       </c>
       <c r="I55" t="n">
         <v>16.55121768438931</v>
       </c>
       <c r="J55" t="n">
-        <v>2.822867214489756</v>
+        <v>2.746157412436054</v>
       </c>
       <c r="K55" t="n">
         <v>16.55121768438931</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>3.069807790763183</v>
+        <v>3.007584976284879</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>16.55121768438931</v>
       </c>
       <c r="F56" t="n">
-        <v>3.069807790763183</v>
+        <v>2.728359084910181</v>
       </c>
       <c r="G56" t="n">
         <v>16.55121768438931</v>
       </c>
       <c r="H56" t="n">
-        <v>2.822386787934255</v>
+        <v>2.974723071696799</v>
       </c>
       <c r="I56" t="n">
         <v>16.55121768438931</v>
       </c>
       <c r="J56" t="n">
-        <v>2.822867214489756</v>
+        <v>2.746157412436054</v>
       </c>
       <c r="K56" t="n">
         <v>16.55121768438931</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>4.137923031963456</v>
+        <v>1.931661804958511</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>16.55121768438931</v>
       </c>
       <c r="F64" t="n">
-        <v>3.89786801592947</v>
+        <v>2.112810567293514</v>
       </c>
       <c r="G64" t="n">
         <v>16.55121768438931</v>
       </c>
       <c r="H64" t="n">
-        <v>4.236218700920489</v>
+        <v>1.939201469963076</v>
       </c>
       <c r="I64" t="n">
         <v>16.55121768438931</v>
       </c>
       <c r="J64" t="n">
-        <v>4.030588312066409</v>
+        <v>2.105422765415053</v>
       </c>
       <c r="K64" t="n">
         <v>16.55121768438931</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>4.242811391277627</v>
+        <v>2.138591206675535</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>16.55121768438931</v>
       </c>
       <c r="F65" t="n">
-        <v>4.096118313353127</v>
+        <v>2.416817639805667</v>
       </c>
       <c r="G65" t="n">
         <v>16.55121768438931</v>
       </c>
       <c r="H65" t="n">
-        <v>4.490232392021588</v>
+        <v>2.189803347485751</v>
       </c>
       <c r="I65" t="n">
         <v>16.55121768438931</v>
       </c>
       <c r="J65" t="n">
-        <v>4.343058889626555</v>
+        <v>2.415520155517209</v>
       </c>
       <c r="K65" t="n">
         <v>16.55121768438931</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>4.730619479485263</v>
+        <v>2.138591206675535</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>16.55121768438931</v>
       </c>
       <c r="F66" t="n">
-        <v>4.71545629995999</v>
+        <v>2.416817639805667</v>
       </c>
       <c r="G66" t="n">
         <v>16.55121768438931</v>
       </c>
       <c r="H66" t="n">
-        <v>4.978040479397804</v>
+        <v>2.189803347485751</v>
       </c>
       <c r="I66" t="n">
         <v>16.55121768438931</v>
       </c>
       <c r="J66" t="n">
-        <v>4.962396876233417</v>
+        <v>2.415520155517209</v>
       </c>
       <c r="K66" t="n">
         <v>16.55121768438931</v>
